--- a/models/summary_20260906.xlsx
+++ b/models/summary_20260906.xlsx
@@ -54,7 +54,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -71,12 +71,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
         <bgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -106,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -125,12 +119,7 @@
     <xf numFmtId="165" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1310,38 +1299,52 @@
       <c r="L20" s="7" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="16" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>3401</t>
         </is>
       </c>
-      <c r="B21" s="16" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>帝人</t>
         </is>
       </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>B(観測窓にミッドサイクル不在)</t>
-        </is>
-      </c>
-      <c r="D21" s="16" t="inlineStr">
-        <is>
-          <t>queued</t>
-        </is>
-      </c>
-      <c r="E21" s="16" t="n"/>
-      <c r="F21" s="16" t="n"/>
-      <c r="G21" s="16" t="inlineStr"/>
-      <c r="H21" s="16" t="n"/>
-      <c r="I21" s="16" t="n"/>
-      <c r="J21" s="16" t="inlineStr"/>
-      <c r="K21" s="16" t="inlineStr"/>
-      <c r="L21" s="17" t="inlineStr">
-        <is>
-          <t>型B。追補15 §4-2 の優先順で再判定した。(1) データ起因ではない —— 有報 S100YCMK は取得済み。ただし**IFRS 移行が第159期(FY2025/3)で、IFRS ベースの系列は3期しか存在しない**: 税引前損失 -5,138 / -78,038 / -74,060(FY2024/3〜FY2026/3)。うえに『IT』事業を非継続事業に分類しており、継続事業ベースの過去系列が3期に限られる。(2) 3期すべてが税引前赤字で、観測窓にミッドサイクルが1期も存在しない。正常化利益の基点を観測窓の外から持ち込むことになるため §Y により置けない。(3) 型A フォールバックも基点が負のため成立しない。【欠落データ（1件）】継続事業ベースで黒字だった期を含む営業利益系列（IFRS 遡及適用の追加開示）、または会社の中期経営計画の正常化営業利益。</t>
-        </is>
-      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>1737</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>2615</v>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H21" s="8" t="n">
+        <v>0.5054999999999999</v>
+      </c>
+      <c r="I21" s="4" t="n"/>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>FAIL 0 / WARN 0 / SKIP 0 / PASS 27</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-07 追補15 追加対応</t>
+        </is>
+      </c>
+      <c r="L21" s="7" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
@@ -2858,38 +2861,52 @@
       <c r="L54" s="15" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="16" t="inlineStr">
+      <c r="A55" s="10" t="inlineStr">
         <is>
           <t>6326</t>
         </is>
       </c>
-      <c r="B55" s="16" t="inlineStr">
+      <c r="B55" s="10" t="inlineStr">
         <is>
           <t>クボタ</t>
         </is>
       </c>
-      <c r="C55" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D55" s="16" t="inlineStr">
-        <is>
-          <t>queued</t>
-        </is>
-      </c>
-      <c r="E55" s="16" t="n"/>
-      <c r="F55" s="16" t="n"/>
-      <c r="G55" s="16" t="inlineStr"/>
-      <c r="H55" s="16" t="n"/>
-      <c r="I55" s="16" t="n"/>
-      <c r="J55" s="16" t="inlineStr"/>
-      <c r="K55" s="16" t="inlineStr"/>
-      <c r="L55" s="17" t="inlineStr">
-        <is>
-          <t>型C。追補15 A-0 の再スクリーンで金融資産 35.8%(FinancialReceivables 流動 645,082 + 非流動 1,576,174)が検出されたが、報告セグメントは『機械』(売上 2,628,861 / OP 253,638)と『水・環境』(374,385 / 32,983)の2つだけで金融が独立していない。事業/金融の EBIT 分解も金融事業の純資産も取れない。なお A-0 のルーターは型E を推奨するが、クボタの金融はクボタ製品の販売金融(captive finance)であって銀行ではないため**型C のまま**とする(ルーターは C と E を区別できない)。必要: 決算説明資料の販売金融事業の損益・債権残高・有利子負債。</t>
-        </is>
-      </c>
+      <c r="C55" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D55" s="10" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="E55" s="11" t="n">
+        <v>3006</v>
+      </c>
+      <c r="F55" s="12" t="n">
+        <v>1905</v>
+      </c>
+      <c r="G55" s="10" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="H55" s="13" t="n">
+        <v>-0.3663</v>
+      </c>
+      <c r="I55" s="10" t="n"/>
+      <c r="J55" s="10" t="inlineStr">
+        <is>
+          <t>FAIL 0 / WARN 1 / SKIP 0 / PASS 26</t>
+        </is>
+      </c>
+      <c r="K55" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-07 追補15 追加対応</t>
+        </is>
+      </c>
+      <c r="L55" s="15" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
@@ -3962,38 +3979,52 @@
       <c r="L78" s="7" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="16" t="inlineStr">
+      <c r="A79" s="4" t="inlineStr">
         <is>
           <t>7731</t>
         </is>
       </c>
-      <c r="B79" s="16" t="inlineStr">
+      <c r="B79" s="4" t="inlineStr">
         <is>
           <t>ニコン</t>
         </is>
       </c>
-      <c r="C79" s="16" t="inlineStr">
-        <is>
-          <t>B(減損除外後も直近赤字)</t>
-        </is>
-      </c>
-      <c r="D79" s="16" t="inlineStr">
-        <is>
-          <t>queued</t>
-        </is>
-      </c>
-      <c r="E79" s="16" t="n"/>
-      <c r="F79" s="16" t="n"/>
-      <c r="G79" s="16" t="inlineStr"/>
-      <c r="H79" s="16" t="n"/>
-      <c r="I79" s="16" t="n"/>
-      <c r="J79" s="16" t="inlineStr"/>
-      <c r="K79" s="16" t="inlineStr"/>
-      <c r="L79" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">型B。追補15 §4-2 の優先順で再判定した。(1) データ起因ではない —— 有報 S100YKBP の5期指標は取得済み: 税引前利益 57,096 / 57,058 / 42,669 / 4,533 / -106,511(FY2022/3〜FY2026/3)。鮮度緩和は不要。(2) 一過性は特定できた —— FY2026/3 の営業損失 -112,448 のうち 減損損失 99,141(デジタルマニュファクチャリング事業ののれん 54,723 を全額減損)と構造改革関連費用 4,923。**除外後でも営業利益は -8,384 で赤字**（前期 +2,422）。(3) 5期の営業利益は厳密に単調減少しており §AU の単調性ゲートに掛かる。§Y により単調系列のミッドサイクル正常化は禁止のため、正の基点を置けない。型A フォールバックも基点が負のため EV が負になり Target </t>
-        </is>
-      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="E79" s="5" t="n">
+        <v>1880</v>
+      </c>
+      <c r="F79" s="6" t="n">
+        <v>1368</v>
+      </c>
+      <c r="G79" s="4" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="H79" s="8" t="n">
+        <v>-0.2723</v>
+      </c>
+      <c r="I79" s="4" t="n"/>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>FAIL 0 / WARN 0 / SKIP 0 / PASS 27</t>
+        </is>
+      </c>
+      <c r="K79" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-07 追補15 追加対応</t>
+        </is>
+      </c>
+      <c r="L79" s="7" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="10" t="inlineStr">
@@ -5452,25 +5483,25 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>0</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F4" s="4" t="n">
         <v>5</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>-0.17065</v>
+        <v>-0.2115</v>
       </c>
     </row>
     <row r="5">
@@ -5480,13 +5511,13 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>12</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>3</v>
@@ -5536,13 +5567,13 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" s="4" t="n">
         <v>0</v>
@@ -5631,7 +5662,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E72"/>
+  <dimension ref="A1:E70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -5703,7 +5734,7 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E5" s="18" t="inlineStr">
+      <c r="E5" s="16" t="inlineStr">
         <is>
           <t>11. PGM-implied vs assumed exit multiple PGM implies 4.97x vs assumed 10.90x (2.19x apart) — the two DCF legs disagree on terminal value</t>
         </is>
@@ -5730,48 +5761,48 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E6" s="18" t="inlineStr">
+      <c r="E6" s="16" t="inlineStr">
         <is>
           <t>11. PGM-implied vs assumed exit multiple PGM implies 5.27x vs assumed 10.50x (1.99x apart) — the two DCF legs disagree on terminal value</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="inlineStr">
-        <is>
-          <t>3401</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>帝人</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>B(観測窓にミッドサイクル不在)</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>queued</t>
-        </is>
-      </c>
-      <c r="E7" s="19" t="inlineStr">
-        <is>
-          <t>[キュー維持] 型B。追補15 §4-2 の優先順で再判定した。(1) データ起因ではない —— 有報 S100YCMK は取得済み。ただし**IFRS 移行が第159期(FY2025/3)で、IFRS ベースの系列は3期しか存在しない**: 税引前損失 -5,138 / -78,038 / -74,060(FY2024/3〜FY2026/3)。うえに『IT』事業を非継続事業に分類しており、継続事業ベースの過去系列が3期に限られる。(2) 3期すべてが税引前赤字で、観測窓にミッドサイクルが1期も存在しない。正常化利益の基点を観測窓の外から持ち込むことになるため §Y により置けない。(3) 型A フォールバックも基点が負のため成立しない。【欠落データ（1件）】継続事業ベースで黒字だった期を含む営業利益系列（IFRS 遡及適用の追加開示）、または会社の中期経営計画の正常化営業利益。</t>
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>3405</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>クラレ</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
+        <is>
+          <t>11. PGM-implied vs assumed exit multiple PGM implies 4.42x vs assumed 8.70x (1.97x apart) — the two DCF legs disagree on terminal value</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>3405</t>
+          <t>3407</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>クラレ</t>
+          <t>旭化成</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
@@ -5784,26 +5815,26 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E8" s="18" t="inlineStr">
-        <is>
-          <t>11. PGM-implied vs assumed exit multiple PGM implies 4.42x vs assumed 8.70x (1.97x apart) — the two DCF legs disagree on terminal value</t>
+      <c r="E8" s="16" t="inlineStr">
+        <is>
+          <t>11. PGM-implied vs assumed exit multiple PGM implies 4.34x vs assumed 9.20x (2.12x apart) — the two DCF legs disagree on terminal value</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>3407</t>
+          <t>3659</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>旭化成</t>
+          <t>ネクソン</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr">
@@ -5811,26 +5842,26 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E9" s="18" t="inlineStr">
-        <is>
-          <t>11. PGM-implied vs assumed exit multiple PGM implies 4.34x vs assumed 9.20x (2.12x apart) — the two DCF legs disagree on terminal value</t>
+      <c r="E9" s="16" t="inlineStr">
+        <is>
+          <t>11. PGM-implied vs assumed exit multiple PGM implies 7.77x vs assumed 15.50x (1.99x apart) — the two DCF legs disagree on terminal value</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>3659</t>
+          <t>4005</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>ネクソン</t>
+          <t>住友化学</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr">
@@ -5838,21 +5869,21 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E10" s="18" t="inlineStr">
-        <is>
-          <t>11. PGM-implied vs assumed exit multiple PGM implies 7.77x vs assumed 15.50x (1.99x apart) — the two DCF legs disagree on terminal value</t>
+      <c r="E10" s="16" t="inlineStr">
+        <is>
+          <t>11. PGM-implied vs assumed exit multiple PGM implies 4.81x vs assumed 8.70x (1.81x apart) — the two DCF legs disagree on terminal value</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>4005</t>
+          <t>4188</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>住友化学</t>
+          <t>三菱ケミカルグループ</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
@@ -5865,26 +5896,26 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E11" s="18" t="inlineStr">
-        <is>
-          <t>11. PGM-implied vs assumed exit multiple PGM implies 4.81x vs assumed 8.70x (1.81x apart) — the two DCF legs disagree on terminal value</t>
+      <c r="E11" s="16" t="inlineStr">
+        <is>
+          <t>11. PGM-implied vs assumed exit multiple PGM implies 2.69x vs assumed 6.50x (2.41x apart) — the two DCF legs disagree on terminal value</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>4188</t>
+          <t>4503</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>三菱ケミカルグループ</t>
+          <t>アステラス製薬</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D12" s="10" t="inlineStr">
@@ -5892,21 +5923,21 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E12" s="18" t="inlineStr">
-        <is>
-          <t>11. PGM-implied vs assumed exit multiple PGM implies 2.69x vs assumed 6.50x (2.41x apart) — the two DCF legs disagree on terminal value</t>
+      <c r="E12" s="16" t="inlineStr">
+        <is>
+          <t>11. PGM-implied vs assumed exit multiple PGM implies 5.21x vs assumed 12.00x (2.30x apart) — the two DCF legs disagree on terminal value</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>4503</t>
+          <t>4523</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>アステラス製薬</t>
+          <t>エーザイ</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
@@ -5919,21 +5950,21 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E13" s="18" t="inlineStr">
-        <is>
-          <t>11. PGM-implied vs assumed exit multiple PGM implies 5.21x vs assumed 12.00x (2.30x apart) — the two DCF legs disagree on terminal value</t>
+      <c r="E13" s="16" t="inlineStr">
+        <is>
+          <t>11. PGM-implied vs assumed exit multiple PGM implies 3.78x vs assumed 10.40x (2.75x apart) — the two DCF legs disagree on terminal value</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>4523</t>
+          <t>4543</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>エーザイ</t>
+          <t>テルモ</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
@@ -5946,26 +5977,26 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E14" s="18" t="inlineStr">
-        <is>
-          <t>11. PGM-implied vs assumed exit multiple PGM implies 3.78x vs assumed 10.40x (2.75x apart) — the two DCF legs disagree on terminal value</t>
+      <c r="E14" s="16" t="inlineStr">
+        <is>
+          <t>11. PGM-implied vs assumed exit multiple PGM implies 5.75x vs assumed 12.60x (2.19x apart) — the two DCF legs disagree on terminal value</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>4543</t>
+          <t>6146</t>
         </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>テルモ</t>
+          <t>ディスコ</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr">
@@ -5973,9 +6004,9 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E15" s="18" t="inlineStr">
-        <is>
-          <t>11. PGM-implied vs assumed exit multiple PGM implies 5.75x vs assumed 12.60x (2.19x apart) — the two DCF legs disagree on terminal value</t>
+      <c r="E15" s="16" t="inlineStr">
+        <is>
+          <t>11. PGM-implied vs assumed exit multiple PGM implies 6.45x vs assumed 38.90x (6.03x apart) — the two DCF legs disagree on terminal value</t>
         </is>
       </c>
     </row>
@@ -6000,26 +6031,26 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E16" s="18" t="inlineStr">
-        <is>
-          <t>11. PGM-implied vs assumed exit multiple PGM implies 6.45x vs assumed 38.90x (6.03x apart) — the two DCF legs disagree on terminal value</t>
+      <c r="E16" s="16" t="inlineStr">
+        <is>
+          <t>14. Target Price averages DCF legs only C10 = =IF(ISNUMBER(C16),ROUND(C16,0),"N/A") does not average C16:C17 - expected when a leg was demoted (追補6 §X) or the Target is a 型D DDM/RI average. No comps row is referenced.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>6146</t>
+          <t>6273</t>
         </is>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>ディスコ</t>
+          <t>SMC</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr">
@@ -6027,9 +6058,9 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E17" s="18" t="inlineStr">
-        <is>
-          <t>14. Target Price averages DCF legs only C10 = =IF(ISNUMBER(C16),ROUND(C16,0),"N/A") does not average C16:C17 - expected when a leg was demoted (追補6 §X) or the Target is a 型D DDM/RI average. No comps row is referenced.</t>
+      <c r="E17" s="16" t="inlineStr">
+        <is>
+          <t>11. PGM-implied vs assumed exit multiple PGM implies 4.65x vs assumed 15.60x (3.35x apart) — the two DCF legs disagree on terminal value</t>
         </is>
       </c>
     </row>
@@ -6054,26 +6085,26 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E18" s="18" t="inlineStr">
-        <is>
-          <t>11. PGM-implied vs assumed exit multiple PGM implies 4.65x vs assumed 15.60x (3.35x apart) — the two DCF legs disagree on terminal value</t>
+      <c r="E18" s="16" t="inlineStr">
+        <is>
+          <t>14. Target Price averages DCF legs only C10 = =IF(ISNUMBER(C17),ROUND(C17,0),"N/A") does not average C16:C17 - expected when a leg was demoted (追補6 §X) or the Target is a 型D DDM/RI average. No comps row is referenced.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>6273</t>
+          <t>6301</t>
         </is>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>SMC</t>
+          <t>コマツ</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C(型F 機構で実装)</t>
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr">
@@ -6081,26 +6112,26 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E19" s="18" t="inlineStr">
-        <is>
-          <t>14. Target Price averages DCF legs only C10 = =IF(ISNUMBER(C17),ROUND(C17,0),"N/A") does not average C16:C17 - expected when a leg was demoted (追補6 §X) or the Target is a 型D DDM/RI average. No comps row is referenced.</t>
+      <c r="E19" s="16" t="inlineStr">
+        <is>
+          <t>26. 型F 持分法投資価値の別途加算 Target C10 = =MAX(0,IFERROR((IF(COUNT(C16:C17)=0,"N/A",ROUND(AVERAGE(C16:C17),0)))*1,0))+C22 に加算行 C22 が入っている; 方式 book_value; Target 3,578 のうち加算脚 1,544 (43%); BS残高 1,390,867 mn; 方式が book_value（BS残高×1.0）— 上場持分先の【簿価】が有報の注記から取得できないため時価への置換ができていない。上場持分に含み益がある分だけ**保守的（過小）**に出る。個別簿価が取れたら listed_stakes へ切り替えること</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>6301</t>
+          <t>6326</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>コマツ</t>
+          <t>クボタ</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>C(型F 機構で実装)</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr">
@@ -6108,36 +6139,36 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E20" s="18" t="inlineStr">
-        <is>
-          <t>26. 型F 持分法投資価値の別途加算 Target C10 = =MAX(0,IFERROR((IF(COUNT(C16:C17)=0,"N/A",ROUND(AVERAGE(C16:C17),0)))*1,0))+C22 に加算行 C22 が入っている; 方式 book_value; Target 3,578 のうち加算脚 1,544 (43%); BS残高 1,390,867 mn; 方式が book_value（BS残高×1.0）— 上場持分先の【簿価】が有報の注記から取得できないため時価への置換ができていない。上場持分に含み益がある分だけ**保守的（過小）**に出る。個別簿価が取れたら listed_stakes へ切り替えること</t>
+      <c r="E20" s="16" t="inlineStr">
+        <is>
+          <t>11. PGM-implied vs assumed exit multiple PGM implies 4.22x vs assumed 9.50x (2.25x apart) — the two DCF legs disagree on terminal value</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="16" t="inlineStr">
-        <is>
-          <t>6326</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t>クボタ</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D21" s="16" t="inlineStr">
-        <is>
-          <t>queued</t>
-        </is>
-      </c>
-      <c r="E21" s="19" t="inlineStr">
-        <is>
-          <t>[キュー維持] 型C。追補15 A-0 の再スクリーンで金融資産 35.8%(FinancialReceivables 流動 645,082 + 非流動 1,576,174)が検出されたが、報告セグメントは『機械』(売上 2,628,861 / OP 253,638)と『水・環境』(374,385 / 32,983)の2つだけで金融が独立していない。事業/金融の EBIT 分解も金融事業の純資産も取れない。なお A-0 のルーターは型E を推奨するが、クボタの金融はクボタ製品の販売金融(captive finance)であって銀行ではないため**型C のまま**とする(ルーターは C と E を区別できない)。必要: 決算説明資料の販売金融事業の損益・債権残高・有利子負債。</t>
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>6367</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>ダイキン工業</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="E21" s="16" t="inlineStr">
+        <is>
+          <t>11. PGM-implied vs assumed exit multiple PGM implies 4.32x vs assumed 14.30x (3.31x apart) — the two DCF legs disagree on terminal value</t>
         </is>
       </c>
     </row>
@@ -6162,21 +6193,21 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E22" s="18" t="inlineStr">
-        <is>
-          <t>11. PGM-implied vs assumed exit multiple PGM implies 4.32x vs assumed 14.30x (3.31x apart) — the two DCF legs disagree on terminal value</t>
+      <c r="E22" s="16" t="inlineStr">
+        <is>
+          <t>14. Target Price averages DCF legs only C10 = =IF(ISNUMBER(C17),ROUND(C17,0),"N/A") does not average C16:C17 - expected when a leg was demoted (追補6 §X) or the Target is a 型D DDM/RI average. No comps row is referenced.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>6367</t>
+          <t>6479</t>
         </is>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>ダイキン工業</t>
+          <t>ミネベアミツミ</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
@@ -6189,21 +6220,21 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E23" s="18" t="inlineStr">
-        <is>
-          <t>14. Target Price averages DCF legs only C10 = =IF(ISNUMBER(C17),ROUND(C17,0),"N/A") does not average C16:C17 - expected when a leg was demoted (追補6 §X) or the Target is a 型D DDM/RI average. No comps row is referenced.</t>
+      <c r="E23" s="16" t="inlineStr">
+        <is>
+          <t>11. PGM-implied vs assumed exit multiple PGM implies 3.76x vs assumed 11.10x (2.96x apart) — the two DCF legs disagree on terminal value</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>6479</t>
+          <t>6501</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>ミネベアミツミ</t>
+          <t>日立製作所</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
@@ -6216,9 +6247,9 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E24" s="18" t="inlineStr">
-        <is>
-          <t>11. PGM-implied vs assumed exit multiple PGM implies 3.76x vs assumed 11.10x (2.96x apart) — the two DCF legs disagree on terminal value</t>
+      <c r="E24" s="16" t="inlineStr">
+        <is>
+          <t>11. PGM-implied vs assumed exit multiple PGM implies 4.10x vs assumed 15.60x (3.81x apart) — the two DCF legs disagree on terminal value</t>
         </is>
       </c>
     </row>
@@ -6243,21 +6274,21 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E25" s="18" t="inlineStr">
-        <is>
-          <t>11. PGM-implied vs assumed exit multiple PGM implies 4.10x vs assumed 15.60x (3.81x apart) — the two DCF legs disagree on terminal value</t>
+      <c r="E25" s="16" t="inlineStr">
+        <is>
+          <t>14. Target Price averages DCF legs only C10 = =IF(ISNUMBER(C17),ROUND(C17,0),"N/A") does not average C16:C17 - expected when a leg was demoted (追補6 §X) or the Target is a 型D DDM/RI average. No comps row is referenced.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>6501</t>
+          <t>6503</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>日立製作所</t>
+          <t>三菱電機</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
@@ -6270,9 +6301,9 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E26" s="18" t="inlineStr">
-        <is>
-          <t>14. Target Price averages DCF legs only C10 = =IF(ISNUMBER(C17),ROUND(C17,0),"N/A") does not average C16:C17 - expected when a leg was demoted (追補6 §X) or the Target is a 型D DDM/RI average. No comps row is referenced.</t>
+      <c r="E26" s="16" t="inlineStr">
+        <is>
+          <t>11. PGM-implied vs assumed exit multiple PGM implies 3.50x vs assumed 14.30x (4.08x apart) — the two DCF legs disagree on terminal value</t>
         </is>
       </c>
     </row>
@@ -6297,26 +6328,26 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E27" s="18" t="inlineStr">
-        <is>
-          <t>11. PGM-implied vs assumed exit multiple PGM implies 3.50x vs assumed 14.30x (4.08x apart) — the two DCF legs disagree on terminal value</t>
+      <c r="E27" s="16" t="inlineStr">
+        <is>
+          <t>14. Target Price averages DCF legs only C10 = =IF(ISNUMBER(C17),ROUND(C17,0),"N/A") does not average C16:C17 - expected when a leg was demoted (追補6 §X) or the Target is a 型D DDM/RI average. No comps row is referenced.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
         <is>
-          <t>6503</t>
+          <t>6506</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>三菱電機</t>
+          <t>安川電機</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B疑い(分母トラフ型)・要目視レビュー</t>
         </is>
       </c>
       <c r="D28" s="10" t="inlineStr">
@@ -6324,9 +6355,9 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E28" s="18" t="inlineStr">
-        <is>
-          <t>14. Target Price averages DCF legs only C10 = =IF(ISNUMBER(C17),ROUND(C17,0),"N/A") does not average C16:C17 - expected when a leg was demoted (追補6 §X) or the Target is a 型D DDM/RI average. No comps row is referenced.</t>
+      <c r="E28" s="16" t="inlineStr">
+        <is>
+          <t>11. PGM-implied vs assumed exit multiple PGM implies 3.31x vs assumed 15.00x (4.53x apart) — the two DCF legs disagree on terminal value</t>
         </is>
       </c>
     </row>
@@ -6351,26 +6382,26 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E29" s="18" t="inlineStr">
-        <is>
-          <t>11. PGM-implied vs assumed exit multiple PGM implies 3.31x vs assumed 15.00x (4.53x apart) — the two DCF legs disagree on terminal value</t>
+      <c r="E29" s="16" t="inlineStr">
+        <is>
+          <t>14. Target Price averages DCF legs only C10 = =IF(ISNUMBER(C17),ROUND(C17,0),"N/A") does not average C16:C17 - expected when a leg was demoted (追補6 §X) or the Target is a 型D DDM/RI average. No comps row is referenced.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t>6506</t>
+          <t>6594</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>安川電機</t>
+          <t>ニデック</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>B疑い(分母トラフ型)・要目視レビュー</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D30" s="10" t="inlineStr">
@@ -6378,9 +6409,9 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E30" s="18" t="inlineStr">
-        <is>
-          <t>14. Target Price averages DCF legs only C10 = =IF(ISNUMBER(C17),ROUND(C17,0),"N/A") does not average C16:C17 - expected when a leg was demoted (追補6 §X) or the Target is a 型D DDM/RI average. No comps row is referenced.</t>
+      <c r="E30" s="16" t="inlineStr">
+        <is>
+          <t>9. Terminal-year capex / D&amp;A ratio 0.87x outside [0.90, 1.15] at g=1.00% — perpetuity assumes this capex forever (analyst call, not auto-fixed)</t>
         </is>
       </c>
     </row>
@@ -6405,9 +6436,9 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E31" s="18" t="inlineStr">
-        <is>
-          <t>9. Terminal-year capex / D&amp;A ratio 0.87x outside [0.90, 1.15] at g=1.00% — perpetuity assumes this capex forever (analyst call, not auto-fixed)</t>
+      <c r="E31" s="16" t="inlineStr">
+        <is>
+          <t>11. PGM-implied vs assumed exit multiple PGM implies 5.75x vs assumed 15.60x (2.71x apart) — the two DCF legs disagree on terminal value</t>
         </is>
       </c>
     </row>
@@ -6432,21 +6463,21 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E32" s="18" t="inlineStr">
-        <is>
-          <t>11. PGM-implied vs assumed exit multiple PGM implies 5.75x vs assumed 15.60x (2.71x apart) — the two DCF legs disagree on terminal value</t>
+      <c r="E32" s="16" t="inlineStr">
+        <is>
+          <t>23. Disclosure vintage recorded 最新の確定年次開示 2025-03-31（分析基準日から 18 か月前） / 年次 docID: 2025-03-31=S100WRH7, 2024-03-31=S100TNGX, 2023-03-31=S100R0SZ, 2022-03-31=S100OA6Q, 2021-03-31=S100LMP5 / 半期 docID: 2026-03-31=S100X4KI — 追補13 §A の鮮度緩和が適用された状態。最新期の確定開示が出たら再生成すること</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>6594</t>
+          <t>6645</t>
         </is>
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>ニデック</t>
+          <t>オムロン</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
@@ -6459,9 +6490,9 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E33" s="18" t="inlineStr">
-        <is>
-          <t>23. Disclosure vintage recorded 最新の確定年次開示 2025-03-31（分析基準日から 18 か月前） / 年次 docID: 2025-03-31=S100WRH7, 2024-03-31=S100TNGX, 2023-03-31=S100R0SZ, 2022-03-31=S100OA6Q, 2021-03-31=S100LMP5 / 半期 docID: 2026-03-31=S100X4KI — 追補13 §A の鮮度緩和が適用された状態。最新期の確定開示が出たら再生成すること</t>
+      <c r="E33" s="16" t="inlineStr">
+        <is>
+          <t>11. PGM-implied vs assumed exit multiple PGM implies 3.71x vs assumed 15.60x (4.21x apart) — the two DCF legs disagree on terminal value</t>
         </is>
       </c>
     </row>
@@ -6486,21 +6517,21 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E34" s="18" t="inlineStr">
-        <is>
-          <t>11. PGM-implied vs assumed exit multiple PGM implies 3.71x vs assumed 15.60x (4.21x apart) — the two DCF legs disagree on terminal value</t>
+      <c r="E34" s="16" t="inlineStr">
+        <is>
+          <t>14. Target Price averages DCF legs only C10 = =IF(ISNUMBER(C17),ROUND(C17,0),"N/A") does not average C16:C17 - expected when a leg was demoted (追補6 §X) or the Target is a 型D DDM/RI average. No comps row is referenced.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>6645</t>
+          <t>6701</t>
         </is>
       </c>
       <c r="B35" s="10" t="inlineStr">
         <is>
-          <t>オムロン</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
@@ -6513,21 +6544,21 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E35" s="18" t="inlineStr">
-        <is>
-          <t>14. Target Price averages DCF legs only C10 = =IF(ISNUMBER(C17),ROUND(C17,0),"N/A") does not average C16:C17 - expected when a leg was demoted (追補6 §X) or the Target is a 型D DDM/RI average. No comps row is referenced.</t>
+      <c r="E35" s="16" t="inlineStr">
+        <is>
+          <t>11. PGM-implied vs assumed exit multiple PGM implies 5.49x vs assumed 15.60x (2.84x apart) — the two DCF legs disagree on terminal value</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>6701</t>
+          <t>6702</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>富士通</t>
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr">
@@ -6540,26 +6571,26 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E36" s="18" t="inlineStr">
-        <is>
-          <t>11. PGM-implied vs assumed exit multiple PGM implies 5.49x vs assumed 15.60x (2.84x apart) — the two DCF legs disagree on terminal value</t>
+      <c r="E36" s="16" t="inlineStr">
+        <is>
+          <t>11. PGM-implied vs assumed exit multiple PGM implies 5.71x vs assumed 15.60x (2.73x apart) — the two DCF legs disagree on terminal value</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>6702</t>
+          <t>6752</t>
         </is>
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>富士通</t>
+          <t>パナソニックHD</t>
         </is>
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B疑い(分母トラフ型)・要目視レビュー</t>
         </is>
       </c>
       <c r="D37" s="10" t="inlineStr">
@@ -6567,9 +6598,9 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E37" s="18" t="inlineStr">
-        <is>
-          <t>11. PGM-implied vs assumed exit multiple PGM implies 5.71x vs assumed 15.60x (2.73x apart) — the two DCF legs disagree on terminal value</t>
+      <c r="E37" s="16" t="inlineStr">
+        <is>
+          <t>11. PGM-implied vs assumed exit multiple PGM implies 2.47x vs assumed 14.30x (5.79x apart) — the two DCF legs disagree on terminal value</t>
         </is>
       </c>
     </row>
@@ -6594,26 +6625,26 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E38" s="18" t="inlineStr">
-        <is>
-          <t>11. PGM-implied vs assumed exit multiple PGM implies 2.47x vs assumed 14.30x (5.79x apart) — the two DCF legs disagree on terminal value</t>
+      <c r="E38" s="16" t="inlineStr">
+        <is>
+          <t>14. Target Price averages DCF legs only C10 = =IF(ISNUMBER(C17),ROUND(C17,0),"N/A") does not average C16:C17 - expected when a leg was demoted (追補6 §X) or the Target is a 型D DDM/RI average. No comps row is referenced.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>6752</t>
+          <t>6762</t>
         </is>
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>パナソニックHD</t>
+          <t>TDK</t>
         </is>
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t>B疑い(分母トラフ型)・要目視レビュー</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D39" s="10" t="inlineStr">
@@ -6621,9 +6652,9 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E39" s="18" t="inlineStr">
-        <is>
-          <t>14. Target Price averages DCF legs only C10 = =IF(ISNUMBER(C17),ROUND(C17,0),"N/A") does not average C16:C17 - expected when a leg was demoted (追補6 §X) or the Target is a 型D DDM/RI average. No comps row is referenced.</t>
+      <c r="E39" s="16" t="inlineStr">
+        <is>
+          <t>11. PGM-implied vs assumed exit multiple PGM implies 2.87x vs assumed 18.10x (6.31x apart) — the two DCF legs disagree on terminal value</t>
         </is>
       </c>
     </row>
@@ -6648,26 +6679,26 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E40" s="18" t="inlineStr">
-        <is>
-          <t>11. PGM-implied vs assumed exit multiple PGM implies 2.87x vs assumed 18.10x (6.31x apart) — the two DCF legs disagree on terminal value</t>
+      <c r="E40" s="16" t="inlineStr">
+        <is>
+          <t>14. Target Price averages DCF legs only C10 = =IF(ISNUMBER(C17),ROUND(C17,0),"N/A") does not average C16:C17 - expected when a leg was demoted (追補6 §X) or the Target is a 型D DDM/RI average. No comps row is referenced.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>6762</t>
+          <t>6857</t>
         </is>
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>TDK</t>
+          <t>アドバンテスト</t>
         </is>
       </c>
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D41" s="10" t="inlineStr">
@@ -6675,9 +6706,9 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E41" s="18" t="inlineStr">
-        <is>
-          <t>14. Target Price averages DCF legs only C10 = =IF(ISNUMBER(C17),ROUND(C17,0),"N/A") does not average C16:C17 - expected when a leg was demoted (追補6 §X) or the Target is a 型D DDM/RI average. No comps row is referenced.</t>
+      <c r="E41" s="16" t="inlineStr">
+        <is>
+          <t>11. PGM-implied vs assumed exit multiple PGM implies 5.08x vs assumed 30.90x (6.08x apart) — the two DCF legs disagree on terminal value</t>
         </is>
       </c>
     </row>
@@ -6702,26 +6733,26 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E42" s="18" t="inlineStr">
-        <is>
-          <t>11. PGM-implied vs assumed exit multiple PGM implies 5.08x vs assumed 30.90x (6.08x apart) — the two DCF legs disagree on terminal value</t>
+      <c r="E42" s="16" t="inlineStr">
+        <is>
+          <t>14. Target Price averages DCF legs only C10 = =IF(ISNUMBER(C16),ROUND(C16,0),"N/A") does not average C16:C17 - expected when a leg was demoted (追補6 §X) or the Target is a 型D DDM/RI average. No comps row is referenced.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>6857</t>
+          <t>6861</t>
         </is>
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>アドバンテスト</t>
+          <t>キーエンス</t>
         </is>
       </c>
       <c r="C43" s="10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D43" s="10" t="inlineStr">
@@ -6729,21 +6760,21 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E43" s="18" t="inlineStr">
-        <is>
-          <t>14. Target Price averages DCF legs only C10 = =IF(ISNUMBER(C16),ROUND(C16,0),"N/A") does not average C16:C17 - expected when a leg was demoted (追補6 §X) or the Target is a 型D DDM/RI average. No comps row is referenced.</t>
+      <c r="E43" s="16" t="inlineStr">
+        <is>
+          <t>11. PGM-implied vs assumed exit multiple PGM implies 7.32x vs assumed 18.30x (2.50x apart) — the two DCF legs disagree on terminal value</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>6861</t>
+          <t>6954</t>
         </is>
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>キーエンス</t>
+          <t>ファナック</t>
         </is>
       </c>
       <c r="C44" s="10" t="inlineStr">
@@ -6756,9 +6787,9 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E44" s="18" t="inlineStr">
-        <is>
-          <t>11. PGM-implied vs assumed exit multiple PGM implies 7.32x vs assumed 18.30x (2.50x apart) — the two DCF legs disagree on terminal value</t>
+      <c r="E44" s="16" t="inlineStr">
+        <is>
+          <t>11. PGM-implied vs assumed exit multiple PGM implies 4.42x vs assumed 15.60x (3.53x apart) — the two DCF legs disagree on terminal value</t>
         </is>
       </c>
     </row>
@@ -6783,26 +6814,26 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E45" s="18" t="inlineStr">
-        <is>
-          <t>11. PGM-implied vs assumed exit multiple PGM implies 4.42x vs assumed 15.60x (3.53x apart) — the two DCF legs disagree on terminal value</t>
+      <c r="E45" s="16" t="inlineStr">
+        <is>
+          <t>14. Target Price averages DCF legs only C10 = =IF(ISNUMBER(C17),ROUND(C17,0),"N/A") does not average C16:C17 - expected when a leg was demoted (追補6 §X) or the Target is a 型D DDM/RI average. No comps row is referenced.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>6954</t>
+          <t>6971</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>ファナック</t>
+          <t>京セラ</t>
         </is>
       </c>
       <c r="C46" s="10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D46" s="10" t="inlineStr">
@@ -6810,26 +6841,26 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E46" s="18" t="inlineStr">
-        <is>
-          <t>14. Target Price averages DCF legs only C10 = =IF(ISNUMBER(C17),ROUND(C17,0),"N/A") does not average C16:C17 - expected when a leg was demoted (追補6 §X) or the Target is a 型D DDM/RI average. No comps row is referenced.</t>
+      <c r="E46" s="16" t="inlineStr">
+        <is>
+          <t>11. PGM-implied vs assumed exit multiple PGM implies 2.90x vs assumed 8.00x (2.76x apart) — the two DCF legs disagree on terminal value</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>6971</t>
+          <t>6976</t>
         </is>
       </c>
       <c r="B47" s="10" t="inlineStr">
         <is>
-          <t>京セラ</t>
+          <t>太陽誘電</t>
         </is>
       </c>
       <c r="C47" s="10" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D47" s="10" t="inlineStr">
@@ -6837,9 +6868,9 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E47" s="18" t="inlineStr">
-        <is>
-          <t>11. PGM-implied vs assumed exit multiple PGM implies 2.90x vs assumed 8.00x (2.76x apart) — the two DCF legs disagree on terminal value</t>
+      <c r="E47" s="16" t="inlineStr">
+        <is>
+          <t>11. PGM-implied vs assumed exit multiple PGM implies 0.93x vs assumed 11.70x (12.57x apart) — the two DCF legs disagree on terminal value</t>
         </is>
       </c>
     </row>
@@ -6864,21 +6895,21 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E48" s="18" t="inlineStr">
-        <is>
-          <t>11. PGM-implied vs assumed exit multiple PGM implies 0.93x vs assumed 11.70x (12.57x apart) — the two DCF legs disagree on terminal value</t>
+      <c r="E48" s="16" t="inlineStr">
+        <is>
+          <t>14. Target Price averages DCF legs only C10 = =IF(ISNUMBER(C17),ROUND(C17,0),"N/A") does not average C16:C17 - expected when a leg was demoted (追補6 §X) or the Target is a 型D DDM/RI average. No comps row is referenced.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>6976</t>
+          <t>6981</t>
         </is>
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t>太陽誘電</t>
+          <t>村田製作所</t>
         </is>
       </c>
       <c r="C49" s="10" t="inlineStr">
@@ -6891,9 +6922,9 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E49" s="18" t="inlineStr">
-        <is>
-          <t>14. Target Price averages DCF legs only C10 = =IF(ISNUMBER(C17),ROUND(C17,0),"N/A") does not average C16:C17 - expected when a leg was demoted (追補6 §X) or the Target is a 型D DDM/RI average. No comps row is referenced.</t>
+      <c r="E49" s="16" t="inlineStr">
+        <is>
+          <t>11. PGM-implied vs assumed exit multiple PGM implies 2.98x vs assumed 17.20x (5.78x apart) — the two DCF legs disagree on terminal value</t>
         </is>
       </c>
     </row>
@@ -6918,21 +6949,21 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E50" s="18" t="inlineStr">
-        <is>
-          <t>11. PGM-implied vs assumed exit multiple PGM implies 2.98x vs assumed 17.20x (5.78x apart) — the two DCF legs disagree on terminal value</t>
+      <c r="E50" s="16" t="inlineStr">
+        <is>
+          <t>14. Target Price averages DCF legs only C10 = =IF(ISNUMBER(C17),ROUND(C17,0),"N/A") does not average C16:C17 - expected when a leg was demoted (追補6 §X) or the Target is a 型D DDM/RI average. No comps row is referenced.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>6981</t>
+          <t>7011</t>
         </is>
       </c>
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>村田製作所</t>
+          <t>三菱重工業</t>
         </is>
       </c>
       <c r="C51" s="10" t="inlineStr">
@@ -6945,9 +6976,9 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E51" s="18" t="inlineStr">
-        <is>
-          <t>14. Target Price averages DCF legs only C10 = =IF(ISNUMBER(C17),ROUND(C17,0),"N/A") does not average C16:C17 - expected when a leg was demoted (追補6 §X) or the Target is a 型D DDM/RI average. No comps row is referenced.</t>
+      <c r="E51" s="16" t="inlineStr">
+        <is>
+          <t>11. PGM-implied vs assumed exit multiple PGM implies 3.95x vs assumed 12.40x (3.14x apart) — the two DCF legs disagree on terminal value</t>
         </is>
       </c>
     </row>
@@ -6972,21 +7003,21 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E52" s="18" t="inlineStr">
-        <is>
-          <t>11. PGM-implied vs assumed exit multiple PGM implies 3.95x vs assumed 12.40x (3.14x apart) — the two DCF legs disagree on terminal value</t>
+      <c r="E52" s="16" t="inlineStr">
+        <is>
+          <t>14. Target Price averages DCF legs only C10 = =IF(ISNUMBER(C17),ROUND(C17,0),"N/A") does not average C16:C17 - expected when a leg was demoted (追補6 §X) or the Target is a 型D DDM/RI average. No comps row is referenced.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>7011</t>
+          <t>7012</t>
         </is>
       </c>
       <c r="B53" s="10" t="inlineStr">
         <is>
-          <t>三菱重工業</t>
+          <t>川崎重工業</t>
         </is>
       </c>
       <c r="C53" s="10" t="inlineStr">
@@ -6999,9 +7030,9 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E53" s="18" t="inlineStr">
-        <is>
-          <t>14. Target Price averages DCF legs only C10 = =IF(ISNUMBER(C17),ROUND(C17,0),"N/A") does not average C16:C17 - expected when a leg was demoted (追補6 §X) or the Target is a 型D DDM/RI average. No comps row is referenced.</t>
+      <c r="E53" s="16" t="inlineStr">
+        <is>
+          <t>11. PGM-implied vs assumed exit multiple PGM implies 2.61x vs assumed 12.40x (4.75x apart) — the two DCF legs disagree on terminal value</t>
         </is>
       </c>
     </row>
@@ -7026,26 +7057,26 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E54" s="18" t="inlineStr">
-        <is>
-          <t>11. PGM-implied vs assumed exit multiple PGM implies 2.61x vs assumed 12.40x (4.75x apart) — the two DCF legs disagree on terminal value</t>
+      <c r="E54" s="16" t="inlineStr">
+        <is>
+          <t>14. Target Price averages DCF legs only C10 = =IF(ISNUMBER(C17),ROUND(C17,0),"N/A") does not average C16:C17 - expected when a leg was demoted (追補6 §X) or the Target is a 型D DDM/RI average. No comps row is referenced.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>7012</t>
+          <t>7013</t>
         </is>
       </c>
       <c r="B55" s="10" t="inlineStr">
         <is>
-          <t>川崎重工業</t>
+          <t>IHI</t>
         </is>
       </c>
       <c r="C55" s="10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D55" s="10" t="inlineStr">
@@ -7053,9 +7084,9 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E55" s="18" t="inlineStr">
-        <is>
-          <t>14. Target Price averages DCF legs only C10 = =IF(ISNUMBER(C17),ROUND(C17,0),"N/A") does not average C16:C17 - expected when a leg was demoted (追補6 §X) or the Target is a 型D DDM/RI average. No comps row is referenced.</t>
+      <c r="E55" s="16" t="inlineStr">
+        <is>
+          <t>11. PGM-implied vs assumed exit multiple PGM implies 3.34x vs assumed 14.30x (4.28x apart) — the two DCF legs disagree on terminal value</t>
         </is>
       </c>
     </row>
@@ -7080,26 +7111,26 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E56" s="18" t="inlineStr">
-        <is>
-          <t>11. PGM-implied vs assumed exit multiple PGM implies 3.34x vs assumed 14.30x (4.28x apart) — the two DCF legs disagree on terminal value</t>
+      <c r="E56" s="16" t="inlineStr">
+        <is>
+          <t>14. Target Price averages DCF legs only C10 = =IF(ISNUMBER(C17),ROUND(C17,0),"N/A") does not average C16:C17 - expected when a leg was demoted (追補6 §X) or the Target is a 型D DDM/RI average. No comps row is referenced.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>7013</t>
+          <t>7733</t>
         </is>
       </c>
       <c r="B57" s="10" t="inlineStr">
         <is>
-          <t>IHI</t>
+          <t>オリンパス</t>
         </is>
       </c>
       <c r="C57" s="10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D57" s="10" t="inlineStr">
@@ -7107,48 +7138,48 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E57" s="18" t="inlineStr">
-        <is>
-          <t>14. Target Price averages DCF legs only C10 = =IF(ISNUMBER(C17),ROUND(C17,0),"N/A") does not average C16:C17 - expected when a leg was demoted (追補6 §X) or the Target is a 型D DDM/RI average. No comps row is referenced.</t>
+      <c r="E57" s="16" t="inlineStr">
+        <is>
+          <t>11. PGM-implied vs assumed exit multiple PGM implies 5.27x vs assumed 13.60x (2.58x apart) — the two DCF legs disagree on terminal value</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="16" t="inlineStr">
-        <is>
-          <t>7731</t>
-        </is>
-      </c>
-      <c r="B58" s="16" t="inlineStr">
-        <is>
-          <t>ニコン</t>
-        </is>
-      </c>
-      <c r="C58" s="16" t="inlineStr">
-        <is>
-          <t>B(減損除外後も直近赤字)</t>
-        </is>
-      </c>
-      <c r="D58" s="16" t="inlineStr">
-        <is>
-          <t>queued</t>
-        </is>
-      </c>
-      <c r="E58" s="19" t="inlineStr">
-        <is>
-          <t>[キュー維持] 型B。追補15 §4-2 の優先順で再判定した。(1) データ起因ではない —— 有報 S100YKBP の5期指標は取得済み: 税引前利益 57,096 / 57,058 / 42,669 / 4,533 / -106,511(FY2022/3〜FY2026/3)。鮮度緩和は不要。(2) 一過性は特定できた —— FY2026/3 の営業損失 -112,448 のうち 減損損失 99,141(デジタルマニュファクチャリング事業ののれん 54,723 を全額減損)と構造改革関連費用 4,923。**除外後でも営業利益は -8,384 で赤字**（前期 +2,422）。(3) 5期の営業利益は厳密に単調減少しており §AU の単調性ゲートに掛かる。§Y により単調系列のミッドサイクル正常化は禁止のため、正の基点を置けない。型A フォールバックも基点が負のため EV が負になり Target が算定不能。【欠落データ（1件）】新中期経営計画（2022-2025年度は終了済）の営業利益目標、またはセグメント別の正常化営業利益。これが1つあれば即日生成できる。</t>
+      <c r="A58" s="10" t="inlineStr">
+        <is>
+          <t>7741</t>
+        </is>
+      </c>
+      <c r="B58" s="10" t="inlineStr">
+        <is>
+          <t>HOYA</t>
+        </is>
+      </c>
+      <c r="C58" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D58" s="10" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="E58" s="16" t="inlineStr">
+        <is>
+          <t>11. PGM-implied vs assumed exit multiple PGM implies 6.65x vs assumed 15.00x (2.26x apart) — the two DCF legs disagree on terminal value</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>7733</t>
+          <t>7752</t>
         </is>
       </c>
       <c r="B59" s="10" t="inlineStr">
         <is>
-          <t>オリンパス</t>
+          <t>リコー</t>
         </is>
       </c>
       <c r="C59" s="10" t="inlineStr">
@@ -7161,26 +7192,26 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E59" s="18" t="inlineStr">
-        <is>
-          <t>11. PGM-implied vs assumed exit multiple PGM implies 5.27x vs assumed 13.60x (2.58x apart) — the two DCF legs disagree on terminal value</t>
+      <c r="E59" s="16" t="inlineStr">
+        <is>
+          <t>11. PGM-implied vs assumed exit multiple PGM implies 3.33x vs assumed 7.70x (2.31x apart) — the two DCF legs disagree on terminal value</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
         <is>
-          <t>7741</t>
+          <t>8001</t>
         </is>
       </c>
       <c r="B60" s="10" t="inlineStr">
         <is>
-          <t>HOYA</t>
+          <t>伊藤忠商事</t>
         </is>
       </c>
       <c r="C60" s="10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D60" s="10" t="inlineStr">
@@ -7188,26 +7219,26 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E60" s="18" t="inlineStr">
-        <is>
-          <t>11. PGM-implied vs assumed exit multiple PGM implies 6.65x vs assumed 15.00x (2.26x apart) — the two DCF legs disagree on terminal value</t>
+      <c r="E60" s="16" t="inlineStr">
+        <is>
+          <t>26. 型F 持分法投資価値の別途加算 Target C10 = =MAX(0,IFERROR((IF(COUNT(C16:C17)=0,"N/A",ROUND(AVERAGE(C16:C17),0)))*1,0))+C22 に加算行 C22 が入っている; 方式 book_value; Target 921 のうち加算脚 587 (64%); BS残高 4,104,790 mn; 方式が book_value（BS残高×1.0）— 上場持分先の【簿価】が有報の注記から取得できないため時価への置換ができていない。上場持分に含み益がある分だけ**保守的（過小）**に出る。個別簿価が取れたら listed_stakes へ切り替えること</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>7752</t>
+          <t>8002</t>
         </is>
       </c>
       <c r="B61" s="10" t="inlineStr">
         <is>
-          <t>リコー</t>
+          <t>丸紅</t>
         </is>
       </c>
       <c r="C61" s="10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D61" s="10" t="inlineStr">
@@ -7215,21 +7246,21 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E61" s="18" t="inlineStr">
-        <is>
-          <t>11. PGM-implied vs assumed exit multiple PGM implies 3.33x vs assumed 7.70x (2.31x apart) — the two DCF legs disagree on terminal value</t>
+      <c r="E61" s="16" t="inlineStr">
+        <is>
+          <t>26. 型F 持分法投資価値の別途加算 Target C10 = =MAX(0,IFERROR((IF(COUNT(C16:C17)=0,"N/A",ROUND(AVERAGE(C16:C17),0)))*1,0))+C22 に加算行 C22 が入っている; 方式 book_value; Target 2,600 のうち加算脚 2,154 (83%); BS残高 3,504,176 mn; 方式が book_value（BS残高×1.0）— 上場持分先の【簿価】が有報の注記から取得できないため時価への置換ができていない。上場持分に含み益がある分だけ**保守的（過小）**に出る。個別簿価が取れたら listed_stakes へ切り替えること</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
         <is>
-          <t>8001</t>
+          <t>8031</t>
         </is>
       </c>
       <c r="B62" s="10" t="inlineStr">
         <is>
-          <t>伊藤忠商事</t>
+          <t>三井物産</t>
         </is>
       </c>
       <c r="C62" s="10" t="inlineStr">
@@ -7242,26 +7273,26 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E62" s="18" t="inlineStr">
-        <is>
-          <t>26. 型F 持分法投資価値の別途加算 Target C10 = =MAX(0,IFERROR((IF(COUNT(C16:C17)=0,"N/A",ROUND(AVERAGE(C16:C17),0)))*1,0))+C22 に加算行 C22 が入っている; 方式 book_value; Target 921 のうち加算脚 587 (64%); BS残高 4,104,790 mn; 方式が book_value（BS残高×1.0）— 上場持分先の【簿価】が有報の注記から取得できないため時価への置換ができていない。上場持分に含み益がある分だけ**保守的（過小）**に出る。個別簿価が取れたら listed_stakes へ切り替えること</t>
+      <c r="E62" s="16" t="inlineStr">
+        <is>
+          <t>26. 型F 持分法投資価値の別途加算 Target C10 = =MAX(0,IFERROR((IF(COUNT(C16:C17)=0,"N/A",ROUND(AVERAGE(C16:C17),0)))*1,0))+C22 に加算行 C22 が入っている; 方式 book_value; Target 2,106 のうち加算脚 1,962 (93%); BS残高 5,560,536 mn; 方式が book_value（BS残高×1.0）— 上場持分先の【簿価】が有報の注記から取得できないため時価への置換ができていない。上場持分に含み益がある分だけ**保守的（過小）**に出る。個別簿価が取れたら listed_stakes へ切り替えること</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>8002</t>
+          <t>8035</t>
         </is>
       </c>
       <c r="B63" s="10" t="inlineStr">
         <is>
-          <t>丸紅</t>
+          <t>東京エレクトロン</t>
         </is>
       </c>
       <c r="C63" s="10" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D63" s="10" t="inlineStr">
@@ -7269,26 +7300,26 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E63" s="18" t="inlineStr">
-        <is>
-          <t>26. 型F 持分法投資価値の別途加算 Target C10 = =MAX(0,IFERROR((IF(COUNT(C16:C17)=0,"N/A",ROUND(AVERAGE(C16:C17),0)))*1,0))+C22 に加算行 C22 が入っている; 方式 book_value; Target 2,600 のうち加算脚 2,154 (83%); BS残高 3,504,176 mn; 方式が book_value（BS残高×1.0）— 上場持分先の【簿価】が有報の注記から取得できないため時価への置換ができていない。上場持分に含み益がある分だけ**保守的（過小）**に出る。個別簿価が取れたら listed_stakes へ切り替えること</t>
+      <c r="E63" s="16" t="inlineStr">
+        <is>
+          <t>11. PGM-implied vs assumed exit multiple PGM implies 5.98x vs assumed 36.10x (6.04x apart) — the two DCF legs disagree on terminal value</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="10" t="inlineStr">
         <is>
-          <t>8031</t>
+          <t>8035</t>
         </is>
       </c>
       <c r="B64" s="10" t="inlineStr">
         <is>
-          <t>三井物産</t>
+          <t>東京エレクトロン</t>
         </is>
       </c>
       <c r="C64" s="10" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D64" s="10" t="inlineStr">
@@ -7296,26 +7327,26 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E64" s="18" t="inlineStr">
-        <is>
-          <t>26. 型F 持分法投資価値の別途加算 Target C10 = =MAX(0,IFERROR((IF(COUNT(C16:C17)=0,"N/A",ROUND(AVERAGE(C16:C17),0)))*1,0))+C22 に加算行 C22 が入っている; 方式 book_value; Target 2,106 のうち加算脚 1,962 (93%); BS残高 5,560,536 mn; 方式が book_value（BS残高×1.0）— 上場持分先の【簿価】が有報の注記から取得できないため時価への置換ができていない。上場持分に含み益がある分だけ**保守的（過小）**に出る。個別簿価が取れたら listed_stakes へ切り替えること</t>
+      <c r="E64" s="16" t="inlineStr">
+        <is>
+          <t>14. Target Price averages DCF legs only C10 = =IF(ISNUMBER(C16),ROUND(C16,0),"N/A") does not average C16:C17 - expected when a leg was demoted (追補6 §X) or the Target is a 型D DDM/RI average. No comps row is referenced.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>8035</t>
+          <t>8053</t>
         </is>
       </c>
       <c r="B65" s="10" t="inlineStr">
         <is>
-          <t>東京エレクトロン</t>
+          <t>住友商事</t>
         </is>
       </c>
       <c r="C65" s="10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D65" s="10" t="inlineStr">
@@ -7323,26 +7354,26 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E65" s="18" t="inlineStr">
-        <is>
-          <t>11. PGM-implied vs assumed exit multiple PGM implies 5.98x vs assumed 36.10x (6.04x apart) — the two DCF legs disagree on terminal value</t>
+      <c r="E65" s="16" t="inlineStr">
+        <is>
+          <t>26. 型F 持分法投資価値の別途加算 Target C10 = =MAX(0,IFERROR((IF(COUNT(C16:C17)=0,"N/A",ROUND(AVERAGE(C16:C17),0)))*1,0))+C22 に加算行 C22 が入っている; 方式 book_value; Target 767 のうち加算脚 695 (91%); BS残高 3,286,754 mn; 方式が book_value（BS残高×1.0）— 上場持分先の【簿価】が有報の注記から取得できないため時価への置換ができていない。上場持分に含み益がある分だけ**保守的（過小）**に出る。個別簿価が取れたら listed_stakes へ切り替えること</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="10" t="inlineStr">
         <is>
-          <t>8035</t>
+          <t>8058</t>
         </is>
       </c>
       <c r="B66" s="10" t="inlineStr">
         <is>
-          <t>東京エレクトロン</t>
+          <t>三菱商事</t>
         </is>
       </c>
       <c r="C66" s="10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D66" s="10" t="inlineStr">
@@ -7350,26 +7381,26 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E66" s="18" t="inlineStr">
-        <is>
-          <t>14. Target Price averages DCF legs only C10 = =IF(ISNUMBER(C16),ROUND(C16,0),"N/A") does not average C16:C17 - expected when a leg was demoted (追補6 §X) or the Target is a 型D DDM/RI average. No comps row is referenced.</t>
+      <c r="E66" s="16" t="inlineStr">
+        <is>
+          <t>26. 型F 持分法投資価値の別途加算 Target C10 = =MAX(0,IFERROR((IF(COUNT(C16:C17)=0,"N/A",ROUND(AVERAGE(C16:C17),0)))*1,0))+C22 に加算行 C22 が入っている; 方式 book_value; Target 1,424 のうち加算脚 1,424 (100%); BS残高 5,213,027 mn; **コアDCF 不成立** — コア脚のエクイティ（EV − net_debt）が負または算定不能でフロア規則により 0 とした。Target は加算脚のみで構成されており、事業そのものの価値は含まれていない。§AF の相対評価として読むこと; さらに加算脚は book_value（BS残高×1.0）で、上場持分の時価置換ができていないため過小側</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>8053</t>
+          <t>9064</t>
         </is>
       </c>
       <c r="B67" s="10" t="inlineStr">
         <is>
-          <t>住友商事</t>
+          <t>ヤマトHD</t>
         </is>
       </c>
       <c r="C67" s="10" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D67" s="10" t="inlineStr">
@@ -7377,21 +7408,21 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E67" s="18" t="inlineStr">
-        <is>
-          <t>26. 型F 持分法投資価値の別途加算 Target C10 = =MAX(0,IFERROR((IF(COUNT(C16:C17)=0,"N/A",ROUND(AVERAGE(C16:C17),0)))*1,0))+C22 に加算行 C22 が入っている; 方式 book_value; Target 767 のうち加算脚 695 (91%); BS残高 3,286,754 mn; 方式が book_value（BS残高×1.0）— 上場持分先の【簿価】が有報の注記から取得できないため時価への置換ができていない。上場持分に含み益がある分だけ**保守的（過小）**に出る。個別簿価が取れたら listed_stakes へ切り替えること</t>
+      <c r="E67" s="16" t="inlineStr">
+        <is>
+          <t>11. PGM-implied vs assumed exit multiple PGM implies 2.97x vs assumed 8.20x (2.76x apart) — the two DCF legs disagree on terminal value</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="10" t="inlineStr">
         <is>
-          <t>8058</t>
+          <t>9101</t>
         </is>
       </c>
       <c r="B68" s="10" t="inlineStr">
         <is>
-          <t>三菱商事</t>
+          <t>日本郵船</t>
         </is>
       </c>
       <c r="C68" s="10" t="inlineStr">
@@ -7404,21 +7435,21 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E68" s="18" t="inlineStr">
-        <is>
-          <t>26. 型F 持分法投資価値の別途加算 Target C10 = =MAX(0,IFERROR((IF(COUNT(C16:C17)=0,"N/A",ROUND(AVERAGE(C16:C17),0)))*1,0))+C22 に加算行 C22 が入っている; 方式 book_value; Target 1,424 のうち加算脚 1,424 (100%); BS残高 5,213,027 mn; **コアDCF 不成立** — コア脚のエクイティ（EV − net_debt）が負または算定不能でフロア規則により 0 とした。Target は加算脚のみで構成されており、事業そのものの価値は含まれていない。§AF の相対評価として読むこと; さらに加算脚は book_value（BS残高×1.0）で、上場持分の時価置換ができていないため過小側</t>
+      <c r="E68" s="16" t="inlineStr">
+        <is>
+          <t>26. 型F 持分法投資価値の別途加算 Target C10 = =MAX(0,IFERROR((IF(COUNT(C16:C17)=0,"N/A",ROUND(AVERAGE(C16:C17),0)))*1,0))+C22 に加算行 C22 が入っている; 方式 book_value; Target 5,818 のうち加算脚 4,530 (78%); BS残高 1,827,915 mn; 方式が book_value（BS残高×1.0）— 上場持分先の【簿価】が有報の注記から取得できないため時価への置換ができていない。上場持分に含み益がある分だけ**保守的（過小）**に出る。個別簿価が取れたら listed_stakes へ切り替えること</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>9064</t>
+          <t>9202</t>
         </is>
       </c>
       <c r="B69" s="10" t="inlineStr">
         <is>
-          <t>ヤマトHD</t>
+          <t>ANAHD</t>
         </is>
       </c>
       <c r="C69" s="10" t="inlineStr">
@@ -7431,26 +7462,26 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E69" s="18" t="inlineStr">
-        <is>
-          <t>11. PGM-implied vs assumed exit multiple PGM implies 2.97x vs assumed 8.20x (2.76x apart) — the two DCF legs disagree on terminal value</t>
+      <c r="E69" s="16" t="inlineStr">
+        <is>
+          <t>11. PGM-implied vs assumed exit multiple PGM implies 5.98x vs assumed 3.10x (1.93x apart) — the two DCF legs disagree on terminal value</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="10" t="inlineStr">
         <is>
-          <t>9101</t>
+          <t>9983</t>
         </is>
       </c>
       <c r="B70" s="10" t="inlineStr">
         <is>
-          <t>日本郵船</t>
+          <t>ファーストリテイリング</t>
         </is>
       </c>
       <c r="C70" s="10" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D70" s="10" t="inlineStr">
@@ -7458,61 +7489,7 @@
           <t>done</t>
         </is>
       </c>
-      <c r="E70" s="18" t="inlineStr">
-        <is>
-          <t>26. 型F 持分法投資価値の別途加算 Target C10 = =MAX(0,IFERROR((IF(COUNT(C16:C17)=0,"N/A",ROUND(AVERAGE(C16:C17),0)))*1,0))+C22 に加算行 C22 が入っている; 方式 book_value; Target 5,818 のうち加算脚 4,530 (78%); BS残高 1,827,915 mn; 方式が book_value（BS残高×1.0）— 上場持分先の【簿価】が有報の注記から取得できないため時価への置換ができていない。上場持分に含み益がある分だけ**保守的（過小）**に出る。個別簿価が取れたら listed_stakes へ切り替えること</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="10" t="inlineStr">
-        <is>
-          <t>9202</t>
-        </is>
-      </c>
-      <c r="B71" s="10" t="inlineStr">
-        <is>
-          <t>ANAHD</t>
-        </is>
-      </c>
-      <c r="C71" s="10" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D71" s="10" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="E71" s="18" t="inlineStr">
-        <is>
-          <t>11. PGM-implied vs assumed exit multiple PGM implies 5.98x vs assumed 3.10x (1.93x apart) — the two DCF legs disagree on terminal value</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="10" t="inlineStr">
-        <is>
-          <t>9983</t>
-        </is>
-      </c>
-      <c r="B72" s="10" t="inlineStr">
-        <is>
-          <t>ファーストリテイリング</t>
-        </is>
-      </c>
-      <c r="C72" s="10" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D72" s="10" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="E72" s="18" t="inlineStr">
+      <c r="E70" s="16" t="inlineStr">
         <is>
           <t>11. PGM-implied vs assumed exit multiple PGM implies 5.33x vs assumed 10.50x (1.97x apart) — the two DCF legs disagree on terminal value</t>
         </is>
